--- a/maintenance/UV_CuringSystem_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/UV_CuringSystem_Maintenance_Tracker_Template.xlsx
@@ -766,8 +766,14 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-03-06</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1008</v>
+      </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">

--- a/maintenance/UV_CuringSystem_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/UV_CuringSystem_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:Z5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,26 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Tracking_Mode_norm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
         </is>
       </c>
     </row>
@@ -615,6 +635,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -695,6 +731,22 @@
           <t>event</t>
         </is>
       </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Quartz liner tube</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -780,6 +832,22 @@
         <is>
           <t>hours</t>
         </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>UV lamp cleaning kit; Optics wipes; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -863,6 +931,22 @@
           <t>calendar</t>
         </is>
       </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Air filter element</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3-Month</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/maintenance/UV_CuringSystem_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/UV_CuringSystem_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z5"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -559,6 +559,21 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -599,9 +614,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Ultra Violet Curing System – F600S / I606 / P600M</t>
@@ -625,11 +637,20 @@
           <t>Methanol hazard – wear impermeable gloves. Ensure UV lamps are OFF and isolated during cleaning.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>event</t>
@@ -650,6 +671,15 @@
       </c>
       <c r="Z2" t="n">
         <v>20</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="3">
@@ -691,9 +721,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Ultra Violet Curing System – F600S / I606 / P600M</t>
@@ -717,15 +744,20 @@
           <t>Allow lamp to cool; handle quartz with clean cotton gloves to avoid contamination.</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>1009</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1009</v>
+      </c>
+      <c r="U3" t="n">
+        <v>93</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>event</t>
@@ -746,6 +778,15 @@
       </c>
       <c r="Z3" t="n">
         <v>45</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="4">
@@ -792,8 +833,6 @@
           <t>lamp_hours</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>Ultra Violet Curing System – F600S / I606 / P600M</t>
@@ -817,17 +856,12 @@
           <t>Electrical isolation required. Cool lamp in STANDBY before servicing.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
       <c r="S4" t="n">
-        <v>1008</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>685</v>
+      </c>
+      <c r="T4" t="n">
+        <v>685</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>hours</t>
@@ -848,6 +882,9 @@
       </c>
       <c r="Z4" t="n">
         <v>20</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>685</v>
       </c>
     </row>
     <row r="5">
@@ -889,7 +926,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>months</t>
@@ -921,11 +957,11 @@
           <t>Isolate electrical power before opening PSU cabinets.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>calendar</t>
